--- a/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
+++ b/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-03T22:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Level</t>
@@ -202,6 +202,12 @@
   </si>
   <si>
     <t>UAT Participant XYK</t>
+  </si>
+  <si>
+    <t>IOM</t>
+  </si>
+  <si>
+    <t>UAT Participant IOM</t>
   </si>
 </sst>
 </file>
@@ -511,7 +517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -660,6 +666,18 @@
       </c>
       <c r="D12" s="2"/>
     </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
+++ b/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T22:38:59+00:00</t>
+    <t>2026-02-04T13:15:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
+++ b/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:15:56+00:00</t>
+    <t>2026-02-04T15:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
+++ b/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:17:54+00:00</t>
+    <t>2026-02-04T18:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
+++ b/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
+++ b/sitepreview/trust/CodeSystem-Participants-UAT.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-01T12:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>Level</t>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>UAT Participant IOM</t>
+  </si>
+  <si>
+    <t>XXQ</t>
+  </si>
+  <si>
+    <t>UAT Participant XXQ</t>
   </si>
 </sst>
 </file>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -678,6 +684,18 @@
       </c>
       <c r="D13" s="2"/>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
